--- a/reports/LeetcodeDaily Report 2 year_2026-09-18.xlsx
+++ b/reports/LeetcodeDaily Report 2 year_2026-09-18.xlsx
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1847,31 +1847,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KITCHAGARI VENKATA RAKESH</t>
+          <t>KIRUBALANI S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LIBINESH R U</t>
+          <t>KITCHAGARI VENKATA RAKESH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+          <t>No usable profile URL in master file</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOKKU KARTHIK</t>
+          <t>LIBINESH R U</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1883,31 +1883,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MADHESH S</t>
+          <t>LOKKU KARTHIK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MADESHWARAN P</t>
+          <t>MADHESH S</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+          <t>No usable profile URL in master file</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MANGALAPURI HARI PRIYA</t>
+          <t>MADESHWARAN P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MARAM BAVESH REDDY</t>
+          <t>MANGALAPURI HARI PRIYA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MONICA S</t>
+          <t>MARAM BAVESH REDDY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MUNNAMGI REVANTH SAI KRISHNA REDDY</t>
+          <t>MONICA S</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NIVETHA G</t>
+          <t>MUNNAMGI REVANTH SAI KRISHNA REDDY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PERUMAL K</t>
+          <t>NIVETHA G</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1979,31 +1979,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRATHIP R L</t>
+          <t>PERUMAL K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRAUSHA N</t>
+          <t>PRATHIP R L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+          <t>No usable profile URL in master file</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PREEJA VARSHINI I K</t>
+          <t>PRAUSHA N</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RIYAS R</t>
+          <t>PREEJA VARSHINI I K</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2027,31 +2027,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SANDHIYA Y</t>
+          <t>RIYAS R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SANTHOSH KUMAR A</t>
+          <t>SANDHIYA Y</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+          <t>No usable profile URL in master file</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SARANYA D</t>
+          <t>SANTHOSH KUMAR A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SATHIYAVAN J</t>
+          <t>SARANYA D</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2075,19 +2075,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIVASANKARI B</t>
+          <t>SATHIYAVAN J</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SRIDHAR V</t>
+          <t>SIVASANKARI B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRINIDHI K</t>
+          <t>SRIDHAR V</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2111,19 +2111,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUDHARSON G</t>
+          <t>SRINIDHI K</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+          <t>No usable profile URL in master file</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUGANTH B</t>
+          <t>SUDHARSON G</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>THARANI R</t>
+          <t>SUGANTH B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>U ROHITH KUMAR</t>
+          <t>THARANI R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VARSHINI T</t>
+          <t>U ROHITH KUMAR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VEMPATI VAMSIKRISHNA</t>
+          <t>VARSHINI T</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2183,10 +2183,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>VEMPATI VAMSIKRISHNA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>VISHNU B</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
